--- a/gateway_controller_testing/testing_and_evaluation/experiments/Experiment_Results_Final.xlsx
+++ b/gateway_controller_testing/testing_and_evaluation/experiments/Experiment_Results_Final.xlsx
@@ -8,21 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\capstone_sandbox\gateway_controller_testing\testing_and_evaluation\experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851B133A-4274-4116-9AD3-A3ED07CF609A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C459EF4-FC39-4AF4-BD38-573FA2A0B1F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Analysis_1MB" sheetId="2" r:id="rId2"/>
-    <sheet name="Analysis_10MB" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
     <t>Data Size</t>
   </si>
@@ -30,82 +29,199 @@
     <t>Concurrency</t>
   </si>
   <si>
+    <t>CPU_Avg_envoycbr-httpfilter-sidecar-865946576c-w97ct</t>
+  </si>
+  <si>
+    <t>CPU_P95_envoycbr-httpfilter-sidecar-865946576c-w97ct</t>
+  </si>
+  <si>
+    <t>CPU_Avg_large-sized-data-server--100mb-7464b68864-ft2n2</t>
+  </si>
+  <si>
+    <t>CPU_P95_large-sized-data-server--100mb-7464b68864-ft2n2</t>
+  </si>
+  <si>
+    <t>CPU_Avg_medium-sized-data-server--10mb-74c9cb477f-jlqkx</t>
+  </si>
+  <si>
+    <t>CPU_P95_medium-sized-data-server--10mb-74c9cb477f-jlqkx</t>
+  </si>
+  <si>
+    <t>CPU_Avg_producer-74b7b9568f-jkj7d</t>
+  </si>
+  <si>
+    <t>CPU_P95_producer-74b7b9568f-jkj7d</t>
+  </si>
+  <si>
+    <t>CPU_Avg_pst-pod-7cccd9887-cpz87</t>
+  </si>
+  <si>
+    <t>CPU_P95_pst-pod-7cccd9887-cpz87</t>
+  </si>
+  <si>
+    <t>CPU_Avg_rabbitmq-b597dd85c-rrbt7</t>
+  </si>
+  <si>
+    <t>CPU_P95_rabbitmq-b597dd85c-rrbt7</t>
+  </si>
+  <si>
+    <t>CPU_Avg_siena-pod-6cb59b7788-sjltt</t>
+  </si>
+  <si>
+    <t>CPU_P95_siena-pod-6cb59b7788-sjltt</t>
+  </si>
+  <si>
+    <t>CPU_Avg_small-sized-data-server--1mb-7c4944b698-cnr45</t>
+  </si>
+  <si>
+    <t>CPU_P95_small-sized-data-server--1mb-7c4944b698-cnr45</t>
+  </si>
+  <si>
+    <t>Mem_Avg_envoycbr-httpfilter-sidecar-865946576c-w97ct</t>
+  </si>
+  <si>
+    <t>Mem_P95_envoycbr-httpfilter-sidecar-865946576c-w97ct</t>
+  </si>
+  <si>
+    <t>Mem_Avg_large-sized-data-server--100mb-7464b68864-ft2n2</t>
+  </si>
+  <si>
+    <t>Mem_P95_large-sized-data-server--100mb-7464b68864-ft2n2</t>
+  </si>
+  <si>
+    <t>Mem_Avg_medium-sized-data-server--10mb-74c9cb477f-jlqkx</t>
+  </si>
+  <si>
+    <t>Mem_P95_medium-sized-data-server--10mb-74c9cb477f-jlqkx</t>
+  </si>
+  <si>
+    <t>Mem_Avg_producer-74b7b9568f-jkj7d</t>
+  </si>
+  <si>
+    <t>Mem_P95_producer-74b7b9568f-jkj7d</t>
+  </si>
+  <si>
     <t>Mem_Avg_pst-pod-7cccd9887-cpz87</t>
   </si>
   <si>
-    <t>Mem_Avg_producer-74b7b9568f-jkj7d</t>
+    <t>Mem_P95_pst-pod-7cccd9887-cpz87</t>
+  </si>
+  <si>
+    <t>Mem_Avg_rabbitmq-b597dd85c-rrbt7</t>
+  </si>
+  <si>
+    <t>Mem_P95_rabbitmq-b597dd85c-rrbt7</t>
   </si>
   <si>
     <t>Mem_Avg_siena-pod-6cb59b7788-sjltt</t>
   </si>
   <si>
+    <t>Mem_P95_siena-pod-6cb59b7788-sjltt</t>
+  </si>
+  <si>
     <t>Mem_Avg_small-sized-data-server--1mb-7c4944b698-cnr45</t>
   </si>
   <si>
-    <t>Mem_Avg_rabbitmq-b597dd85c-rrbt7</t>
-  </si>
-  <si>
-    <t>Mem_Avg_medium-sized-data-server--10mb-74c9cb477f-jlqkx</t>
-  </si>
-  <si>
-    <t>Mem_Avg_large-sized-data-server--100mb-7464b68864-ft2n2</t>
-  </si>
-  <si>
-    <t>Mem_Avg_envoycbr-httpfilter-sidecar-865946576c-w97ct</t>
+    <t>Mem_P95_small-sized-data-server--1mb-7c4944b698-cnr45</t>
+  </si>
+  <si>
+    <t>Rate_CPU_Avg_envoycbr-httpfilter-sidecar-865946576c-w97ct</t>
+  </si>
+  <si>
+    <t>Rate_CPU_P95_envoycbr-httpfilter-sidecar-865946576c-w97ct</t>
+  </si>
+  <si>
+    <t>Rate_CPU_Avg_large-sized-data-server--100mb-7464b68864-ft2n2</t>
+  </si>
+  <si>
+    <t>Rate_CPU_P95_large-sized-data-server--100mb-7464b68864-ft2n2</t>
+  </si>
+  <si>
+    <t>Rate_CPU_Avg_medium-sized-data-server--10mb-74c9cb477f-jlqkx</t>
+  </si>
+  <si>
+    <t>Rate_CPU_P95_medium-sized-data-server--10mb-74c9cb477f-jlqkx</t>
+  </si>
+  <si>
+    <t>Rate_CPU_Avg_producer-74b7b9568f-jkj7d</t>
+  </si>
+  <si>
+    <t>Rate_CPU_P95_producer-74b7b9568f-jkj7d</t>
+  </si>
+  <si>
+    <t>Rate_CPU_Avg_pst-pod-7cccd9887-cpz87</t>
+  </si>
+  <si>
+    <t>Rate_CPU_P95_pst-pod-7cccd9887-cpz87</t>
+  </si>
+  <si>
+    <t>Rate_CPU_Avg_rabbitmq-b597dd85c-rrbt7</t>
+  </si>
+  <si>
+    <t>Rate_CPU_P95_rabbitmq-b597dd85c-rrbt7</t>
+  </si>
+  <si>
+    <t>Rate_CPU_Avg_siena-pod-6cb59b7788-sjltt</t>
+  </si>
+  <si>
+    <t>Rate_CPU_P95_siena-pod-6cb59b7788-sjltt</t>
+  </si>
+  <si>
+    <t>Rate_CPU_Avg_small-sized-data-server--1mb-7c4944b698-cnr45</t>
+  </si>
+  <si>
+    <t>Rate_CPU_P95_small-sized-data-server--1mb-7c4944b698-cnr45</t>
+  </si>
+  <si>
+    <t>Rate_Mem_Avg_envoycbr-httpfilter-sidecar-865946576c-w97ct</t>
+  </si>
+  <si>
+    <t>Rate_Mem_P95_envoycbr-httpfilter-sidecar-865946576c-w97ct</t>
+  </si>
+  <si>
+    <t>Rate_Mem_Avg_large-sized-data-server--100mb-7464b68864-ft2n2</t>
+  </si>
+  <si>
+    <t>Rate_Mem_P95_large-sized-data-server--100mb-7464b68864-ft2n2</t>
+  </si>
+  <si>
+    <t>Rate_Mem_Avg_medium-sized-data-server--10mb-74c9cb477f-jlqkx</t>
+  </si>
+  <si>
+    <t>Rate_Mem_P95_medium-sized-data-server--10mb-74c9cb477f-jlqkx</t>
+  </si>
+  <si>
+    <t>Rate_Mem_Avg_producer-74b7b9568f-jkj7d</t>
+  </si>
+  <si>
+    <t>Rate_Mem_P95_producer-74b7b9568f-jkj7d</t>
   </si>
   <si>
     <t>Rate_Mem_Avg_pst-pod-7cccd9887-cpz87</t>
   </si>
   <si>
-    <t>Diff_Mem_Avg_pst-pod-7cccd9887-cpz87</t>
-  </si>
-  <si>
-    <t>Rate_Mem_Avg_producer-74b7b9568f-jkj7d</t>
-  </si>
-  <si>
-    <t>Diff_Mem_Avg_producer-74b7b9568f-jkj7d</t>
+    <t>Rate_Mem_P95_pst-pod-7cccd9887-cpz87</t>
+  </si>
+  <si>
+    <t>Rate_Mem_Avg_rabbitmq-b597dd85c-rrbt7</t>
+  </si>
+  <si>
+    <t>Rate_Mem_P95_rabbitmq-b597dd85c-rrbt7</t>
   </si>
   <si>
     <t>Rate_Mem_Avg_siena-pod-6cb59b7788-sjltt</t>
   </si>
   <si>
-    <t>Diff_Mem_Avg_siena-pod-6cb59b7788-sjltt</t>
+    <t>Rate_Mem_P95_siena-pod-6cb59b7788-sjltt</t>
   </si>
   <si>
     <t>Rate_Mem_Avg_small-sized-data-server--1mb-7c4944b698-cnr45</t>
   </si>
   <si>
-    <t>Diff_Mem_Avg_small-sized-data-server--1mb-7c4944b698-cnr45</t>
-  </si>
-  <si>
-    <t>Rate_Mem_Avg_rabbitmq-b597dd85c-rrbt7</t>
-  </si>
-  <si>
-    <t>Diff_Mem_Avg_rabbitmq-b597dd85c-rrbt7</t>
-  </si>
-  <si>
-    <t>Rate_Mem_Avg_medium-sized-data-server--10mb-74c9cb477f-jlqkx</t>
-  </si>
-  <si>
-    <t>Diff_Mem_Avg_medium-sized-data-server--10mb-74c9cb477f-jlqkx</t>
-  </si>
-  <si>
-    <t>Rate_Mem_Avg_large-sized-data-server--100mb-7464b68864-ft2n2</t>
-  </si>
-  <si>
-    <t>Diff_Mem_Avg_large-sized-data-server--100mb-7464b68864-ft2n2</t>
-  </si>
-  <si>
-    <t>Rate_Mem_Avg_envoycbr-httpfilter-sidecar-865946576c-w97ct</t>
-  </si>
-  <si>
-    <t>Diff_Mem_Avg_envoycbr-httpfilter-sidecar-865946576c-w97ct</t>
+    <t>Rate_Mem_P95_small-sized-data-server--1mb-7c4944b698-cnr45</t>
   </si>
   <si>
     <t>1MB</t>
-  </si>
-  <si>
-    <t>10MB</t>
   </si>
 </sst>
 </file>
@@ -211,7 +327,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Memory Rate of Change (1MB)</a:t>
+              <a:t>Mem Avg Rate of Change (1MB)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -232,23 +348,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -256,21 +375,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$Y$2:$Y$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>0.59299266581632626</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.1055883290816322</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.16565688775510259</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.4199617346938993E-2</c:v>
+              <c:f>Summary!$AY$2:$AY$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.751953125</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.876953125</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.3046875</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.8125E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -278,7 +400,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A052-422B-8531-969897D51B1B}"/>
+              <c16:uniqueId val="{00000000-0370-4049-8807-0C71DB6C8B78}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -290,23 +412,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -314,21 +439,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$W$2:$W$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>2.2959183673492589E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.869897959180889E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.1747448979522233E-3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.7397959183731473E-3</c:v>
+              <c:f>Summary!$BA$2:$BA$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -336,7 +464,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A052-422B-8531-969897D51B1B}"/>
+              <c16:uniqueId val="{00000001-0370-4049-8807-0C71DB6C8B78}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -348,23 +476,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -372,20 +503,23 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$U$2:$U$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
+              <c:f>Summary!$BC$2:$BC$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -394,7 +528,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-A052-422B-8531-969897D51B1B}"/>
+              <c16:uniqueId val="{00000002-0370-4049-8807-0C71DB6C8B78}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -406,23 +540,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -430,21 +567,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$M$2:$M$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>8.0862563775510168</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.0948660714285774</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.2432238520408134</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.176737882653057</c:v>
+              <c:f>Summary!$BE$2:$BE$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.875</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1875</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.18359375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -452,7 +592,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-A052-422B-8531-969897D51B1B}"/>
+              <c16:uniqueId val="{00000003-0370-4049-8807-0C71DB6C8B78}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -464,23 +604,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -488,21 +631,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$K$2:$K$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>0.84518494897959329</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.4607780612244028E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.50159438775510168</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1101721938775526</c:v>
+              <c:f>Summary!$BG$2:$BG$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.375</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.1328125</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.4140625</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.7265625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -510,7 +656,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-A052-422B-8531-969897D51B1B}"/>
+              <c16:uniqueId val="{00000004-0370-4049-8807-0C71DB6C8B78}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -522,23 +668,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -546,21 +695,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$S$2:$S$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>2.1232461734693828</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.123246173469397</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.053970025510196</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-0.87715242346938282</c:v>
+              <c:f>Summary!$BI$2:$BI$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>-0.3776041666666714</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0729166666671404E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.125E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1640625</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-8.984375E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -568,7 +720,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-A052-422B-8531-969897D51B1B}"/>
+              <c16:uniqueId val="{00000005-0370-4049-8807-0C71DB6C8B78}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -580,23 +732,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -604,21 +759,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$O$2:$O$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>0.67255261479590445</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.25362723214288962</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.2959183673435749E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.0009566326564251E-2</c:v>
+              <c:f>Summary!$BK$2:$BK$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>2.34375E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.734375E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5625E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.90625E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5625E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -626,7 +784,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-A052-422B-8531-969897D51B1B}"/>
+              <c16:uniqueId val="{00000006-0370-4049-8807-0C71DB6C8B78}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -638,23 +796,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -662,21 +823,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$Q$2:$Q$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
+              <c:f>Summary!$BM$2:$BM$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.8125E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.90625E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.90625E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -684,7 +848,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-A052-422B-8531-969897D51B1B}"/>
+              <c16:uniqueId val="{00000007-0370-4049-8807-0C71DB6C8B78}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -751,7 +915,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>MiB per extra Req</a:t>
+                  <a:t>Avg MiB/Req</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -808,7 +972,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Absolute Memory Usage (1MB)</a:t>
+              <a:t>Mem P95 Rate of Change (1MB)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -829,23 +993,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -853,24 +1020,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$J$2:$J$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>5.4788743622448983</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.0718670280612246</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.1774553571428568</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.3431122448979593</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.3773118622448983</c:v>
+              <c:f>Summary!$AZ$2:$AZ$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.3287109374999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30019531249999959</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.3046875</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.8125E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -878,7 +1045,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BE3C-4A4C-9FE5-CC82BC254271}"/>
+              <c16:uniqueId val="{00000000-A696-4D5F-B27F-0A2DE94E3651}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -890,23 +1057,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -914,24 +1084,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$I$2:$I$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>285.7734375</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>285.79639668367349</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>285.8250956632653</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>285.83227040816331</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>285.83801020408163</c:v>
+              <c:f>Summary!$BB$2:$BB$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -939,7 +1109,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BE3C-4A4C-9FE5-CC82BC254271}"/>
+              <c16:uniqueId val="{00000001-A696-4D5F-B27F-0A2DE94E3651}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -951,23 +1121,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -975,24 +1148,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$H$2:$H$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>50.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>50.75</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50.75</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>50.75</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>50.75</c:v>
+              <c:f>Summary!$BD$2:$BD$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1000,7 +1173,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-BE3C-4A4C-9FE5-CC82BC254271}"/>
+              <c16:uniqueId val="{00000002-A696-4D5F-B27F-0A2DE94E3651}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1012,23 +1185,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1036,24 +1212,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$D$2:$D$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>26.027503188775508</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>34.113759566326529</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>39.208625637755112</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>46.451849489795919</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>48.628587372448983</c:v>
+              <c:f>Summary!$BF$2:$BF$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.875</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1875</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.18359375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1061,7 +1237,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BE3C-4A4C-9FE5-CC82BC254271}"/>
+              <c16:uniqueId val="{00000003-A696-4D5F-B27F-0A2DE94E3651}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1073,23 +1249,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1097,24 +1276,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$C$2:$C$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>25.881696428571431</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>26.72688137755102</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>26.781489158163261</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>27.28308354591837</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>27.393255739795919</c:v>
+              <c:f>Summary!$BH$2:$BH$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.375</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.1328125</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.4140625</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.7265625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1122,7 +1301,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-BE3C-4A4C-9FE5-CC82BC254271}"/>
+              <c16:uniqueId val="{00000004-A696-4D5F-B27F-0A2DE94E3651}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1134,23 +1313,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1158,24 +1340,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$G$2:$G$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>91.722815688775512</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>93.846061862244895</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>94.969308035714292</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>96.023278061224488</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>95.146125637755105</c:v>
+              <c:f>Summary!$BJ$2:$BJ$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>-0.33984375</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.296875E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.125E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1640625</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-8.984375E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1183,7 +1365,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-BE3C-4A4C-9FE5-CC82BC254271}"/>
+              <c16:uniqueId val="{00000005-A696-4D5F-B27F-0A2DE94E3651}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1195,23 +1377,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1219,24 +1404,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$E$2:$E$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>435.4891581632653</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>436.16171077806121</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>436.4153380102041</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>436.43829719387747</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>436.4583067602041</c:v>
+              <c:f>Summary!$BL$2:$BL$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>2.34375E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.734375E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5625E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.90625E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5625E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1244,7 +1429,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-BE3C-4A4C-9FE5-CC82BC254271}"/>
+              <c16:uniqueId val="{00000006-A696-4D5F-B27F-0A2DE94E3651}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1256,23 +1441,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1280,24 +1468,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$F$2:$F$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>27.51171875</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>27.51171875</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>27.51171875</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>27.51171875</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>27.51171875</c:v>
+              <c:f>Summary!$BN$2:$BN$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.8125E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.90625E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.90625E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1305,7 +1493,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-BE3C-4A4C-9FE5-CC82BC254271}"/>
+              <c16:uniqueId val="{00000007-A696-4D5F-B27F-0A2DE94E3651}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1372,7 +1560,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Total MiB</a:t>
+                  <a:t>P95 MiB/Req</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1429,7 +1617,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Step-over-Step Memory Change (1MB)</a:t>
+              <a:t>CPU Avg Rate of Change (1MB)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1450,23 +1638,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1474,21 +1665,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$Z$2:$Z$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>0.59299266581632626</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.1055883290816322</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.16565688775510259</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.4199617346938993E-2</c:v>
+              <c:f>Summary!$AI$2:$AI$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>2.5576446240656781E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8628041369837529E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.8073763625325318E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-6.382398440053544E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-3.5928076066966432E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1496,7 +1690,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7030-4E72-A543-17D3C909800D}"/>
+              <c16:uniqueId val="{00000000-9038-4188-8D64-287590550F63}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1508,23 +1702,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1532,21 +1729,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$X$2:$X$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>2.2959183673492589E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.869897959180889E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.1747448979522233E-3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.7397959183731473E-3</c:v>
+              <c:f>Summary!$AK$2:$AK$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>1.6368427050392881E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.582515310545487E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.016172150333335E-6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.4896660785131419E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-6.618189762395857E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1554,7 +1754,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7030-4E72-A543-17D3C909800D}"/>
+              <c16:uniqueId val="{00000001-9038-4188-8D64-287590550F63}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1566,23 +1766,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1590,21 +1793,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$V$2:$V$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
+              <c:f>Summary!$AM$2:$AM$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>4.3844811455982021E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.7375241933779841E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-8.8951080907904707E-6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.1376296627782672E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.5978335067999532E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1612,7 +1818,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7030-4E72-A543-17D3C909800D}"/>
+              <c16:uniqueId val="{00000002-9038-4188-8D64-287590550F63}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1624,23 +1830,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1648,21 +1857,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$N$2:$N$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>8.0862563775510168</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.0948660714285774</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.2432238520408134</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.176737882653057</c:v>
+              <c:f>Summary!$AO$2:$AO$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>-5.7146044968302219E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.0197533595553927E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.1095418978106295E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4101212024378201E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.2173633806306429E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1670,7 +1882,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-7030-4E72-A543-17D3C909800D}"/>
+              <c16:uniqueId val="{00000003-9038-4188-8D64-287590550F63}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1682,23 +1894,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1706,21 +1921,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$L$2:$L$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>0.84518494897959329</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.4607780612244028E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.50159438775510168</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1101721938775526</c:v>
+              <c:f>Summary!$AQ$2:$AQ$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>-7.0667973620865175E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.7792365371097917E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.995263747011207E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-3.7442082752624688E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.2899285070764409E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1728,7 +1946,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-7030-4E72-A543-17D3C909800D}"/>
+              <c16:uniqueId val="{00000004-9038-4188-8D64-287590550F63}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1740,23 +1958,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1764,21 +1985,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$T$2:$T$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>2.1232461734693828</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.123246173469397</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.053970025510196</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-0.87715242346938282</c:v>
+              <c:f>Summary!$AS$2:$AS$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>3.2328662135783053E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.3152043348323902E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.0615655249386114E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4350573892926641E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.0084901255605771E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1786,7 +2010,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-7030-4E72-A543-17D3C909800D}"/>
+              <c16:uniqueId val="{00000005-9038-4188-8D64-287590550F63}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1798,23 +2022,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1822,21 +2049,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$P$2:$P$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>0.67255261479590445</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.25362723214288962</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.2959183673435749E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.0009566326564251E-2</c:v>
+              <c:f>Summary!$AU$2:$AU$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>-1.130463313099399E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.340657926619364E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.9527120889032022E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.4603165048320209E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.814927163391099E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1844,7 +2074,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-7030-4E72-A543-17D3C909800D}"/>
+              <c16:uniqueId val="{00000006-9038-4188-8D64-287590550F63}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1856,23 +2086,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1880,21 +2113,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$R$2:$R$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
+              <c:f>Summary!$AW$2:$AW$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>9.1298152283262246E-7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.0450445394492641E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5858986443317321E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.639987959960799E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.1435538960333998E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1902,7 +2138,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-7030-4E72-A543-17D3C909800D}"/>
+              <c16:uniqueId val="{00000007-9038-4188-8D64-287590550F63}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1969,7 +2205,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Delta MiB</a:t>
+                  <a:t>Avg Cores/Req</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2026,7 +2262,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Memory Rate of Change (10MB)</a:t>
+              <a:t>CPU P95 Rate of Change (1MB)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2047,20 +2283,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2068,18 +2310,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$Y$7:$Y$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>5.9470663265306811E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.15864158163265249</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.091358418367367E-2</c:v>
+              <c:f>Summary!$AJ$2:$AJ$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>2.5576446240656781E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5623466618857222E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1078338376305641E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-6.382398440053544E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-3.5928076066966432E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2087,7 +2335,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D8A2-4C7D-AB8F-70A019CF17CB}"/>
+              <c16:uniqueId val="{00000000-BDCE-41A3-8979-CA6B97416384}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2099,20 +2347,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2120,18 +2374,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$W$7:$W$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
+              <c:f>Summary!$AL$2:$AL$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>1.6368427050392881E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.582515310545487E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.016172150333335E-6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.4896660785131419E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-6.618189762395857E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2139,7 +2399,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D8A2-4C7D-AB8F-70A019CF17CB}"/>
+              <c16:uniqueId val="{00000001-BDCE-41A3-8979-CA6B97416384}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2151,20 +2411,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2172,18 +2438,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$U$7:$U$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>1.913265306122014E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.3435905612244881</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-6.73916135204081</c:v>
+              <c:f>Summary!$AN$2:$AN$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>4.3844811455982021E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.4254961969894578E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.201538805467573E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.1376296627782672E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.5978335067999532E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2191,7 +2463,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D8A2-4C7D-AB8F-70A019CF17CB}"/>
+              <c16:uniqueId val="{00000002-BDCE-41A3-8979-CA6B97416384}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2203,20 +2475,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2224,18 +2502,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$M$7:$M$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>4.9372608418367392</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.5815529336734708</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16.02264987244898</c:v>
+              <c:f>Summary!$AP$2:$AP$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>-5.3995498127825081E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.7046986755076788E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.1095418978106295E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4101212024378201E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.2173633806306429E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2243,7 +2527,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-D8A2-4C7D-AB8F-70A019CF17CB}"/>
+              <c16:uniqueId val="{00000003-BDCE-41A3-8979-CA6B97416384}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2255,20 +2539,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2276,18 +2566,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$K$7:$K$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>0.23533163265306101</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.4821428571427049E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.54703124999999986</c:v>
+              <c:f>Summary!$AR$2:$AR$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>-4.0702714425655371E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.2770006564457966E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.79268045829931E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-3.7442082752624688E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.2899285070764409E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2295,7 +2591,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-D8A2-4C7D-AB8F-70A019CF17CB}"/>
+              <c16:uniqueId val="{00000004-BDCE-41A3-8979-CA6B97416384}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2307,20 +2603,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2328,18 +2630,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$S$7:$S$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>3.6485969387755119</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-6.523517219387756</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.164642857142869</c:v>
+              <c:f>Summary!$AT$2:$AT$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>3.4668498714203379E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.5491879926744218E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.0615655249386114E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4350573892926641E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.0084901255605771E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2347,7 +2655,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-D8A2-4C7D-AB8F-70A019CF17CB}"/>
+              <c16:uniqueId val="{00000005-BDCE-41A3-8979-CA6B97416384}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2359,20 +2667,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2380,18 +2694,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$O$7:$O$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>2.606823979590445E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.0487882653071669E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.1058673469422047E-2</c:v>
+              <c:f>Summary!$AV$2:$AV$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>-1.130463313099399E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.340657926619364E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.9527120889032022E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.4603165048320209E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.814927163391099E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2399,7 +2719,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-D8A2-4C7D-AB8F-70A019CF17CB}"/>
+              <c16:uniqueId val="{00000006-BDCE-41A3-8979-CA6B97416384}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2411,20 +2731,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2432,18 +2758,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$Q$7:$Q$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
+              <c:f>Summary!$AX$2:$AX$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>9.1298152283262246E-7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.0450445394492641E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5858986443317321E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.639987959960799E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.1435538960333998E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2451,7 +2783,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-D8A2-4C7D-AB8F-70A019CF17CB}"/>
+              <c16:uniqueId val="{00000007-BDCE-41A3-8979-CA6B97416384}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2518,7 +2850,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>MiB per extra Req</a:t>
+                  <a:t>P95 Cores/Req</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2575,7 +2907,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Absolute Memory Usage (10MB)</a:t>
+              <a:t>Absolute Memory (P95) (1MB)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2596,20 +2928,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2617,21 +2955,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$J$7:$J$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>6.5682397959183669</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.6277104591836737</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.7863520408163263</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.8672656249999999</c:v>
+              <c:f>Summary!$T$2:$T$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5.28125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.28125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.6099609375000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.91015625</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.21484375</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.29296875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2639,7 +2983,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4781-4F8E-8858-D70E93030EA9}"/>
+              <c16:uniqueId val="{00000000-412D-4357-8D52-D2D46ABCF56A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2651,20 +2995,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2672,21 +3022,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$I$7:$I$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>285.84375</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>285.84375</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>285.84375</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>285.84375</c:v>
+              <c:f>Summary!$V$2:$V$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>27.06640625</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27.06640625</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27.06640625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.06640625</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27.06640625</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27.06640625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2694,7 +3050,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4781-4F8E-8858-D70E93030EA9}"/>
+              <c16:uniqueId val="{00000001-412D-4357-8D52-D2D46ABCF56A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2706,20 +3062,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2727,21 +3089,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$H$7:$H$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>50.761001275510203</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>50.762914540816332</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>58.106505102040813</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>51.367343750000003</c:v>
+              <c:f>Summary!$X$2:$X$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>25.72265625</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25.72265625</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.72265625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25.72265625</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.72265625</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25.72265625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2749,7 +3117,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4781-4F8E-8858-D70E93030EA9}"/>
+              <c16:uniqueId val="{00000002-412D-4357-8D52-D2D46ABCF56A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2761,20 +3129,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2782,21 +3156,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$D$7:$D$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>54.735411352040813</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>59.672672193877553</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>63.254225127551017</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>79.276875000000004</c:v>
+              <c:f>Summary!$Z$2:$Z$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>27.45703125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27.45703125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27.45703125</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29.33203125</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29.51953125</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29.703125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2804,7 +3184,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-4781-4F8E-8858-D70E93030EA9}"/>
+              <c16:uniqueId val="{00000003-412D-4357-8D52-D2D46ABCF56A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2816,20 +3196,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2837,21 +3223,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$C$7:$C$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>27.894690688775508</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>28.130022321428569</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>28.21484375</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>28.761875</c:v>
+              <c:f>Summary!$AB$2:$AB$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>25.5390625</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25.5390625</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.9140625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.78125</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.3671875</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31.09375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2859,7 +3251,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-4781-4F8E-8858-D70E93030EA9}"/>
+              <c16:uniqueId val="{00000004-412D-4357-8D52-D2D46ABCF56A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2871,20 +3263,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2892,21 +3290,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$G$7:$G$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>107.1427774234694</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>110.79137436224489</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>104.2678571428571</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>114.4325</c:v>
+              <c:f>Summary!$AD$2:$AD$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>109.58203125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>109.2421875</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>109.28515625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>109.31640625</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>109.48046875</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>109.390625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2914,7 +3318,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-4781-4F8E-8858-D70E93030EA9}"/>
+              <c16:uniqueId val="{00000005-412D-4357-8D52-D2D46ABCF56A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2926,20 +3330,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2947,21 +3357,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$E$7:$E$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>436.49816645408163</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>436.52423469387747</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>436.5447225765306</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>436.58578125000003</c:v>
+              <c:f>Summary!$AF$2:$AF$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>456.3359375</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>456.359375</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>456.38671875</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>456.40234375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>456.44140625</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>456.45703125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2969,7 +3385,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-4781-4F8E-8858-D70E93030EA9}"/>
+              <c16:uniqueId val="{00000006-412D-4357-8D52-D2D46ABCF56A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2981,20 +3397,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3002,21 +3424,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$F$7:$F$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>27.51171875</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>27.51171875</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>27.51171875</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>27.51171875</c:v>
+              <c:f>Summary!$AH$2:$AH$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>30.9140625</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.9140625</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.9140625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.921875</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.92578125</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30.9296875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3024,7 +3452,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-4781-4F8E-8858-D70E93030EA9}"/>
+              <c16:uniqueId val="{00000007-412D-4357-8D52-D2D46ABCF56A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3148,7 +3576,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Step-over-Step Memory Change (10MB)</a:t>
+              <a:t>Absolute CPU (P95) (1MB)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3169,20 +3597,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3190,18 +3624,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$Z$7:$Z$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>5.9470663265306811E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.15864158163265249</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.091358418367367E-2</c:v>
+              <c:f>Summary!$D$2:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5576446240656781E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5879231081263792E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.6957569457569428E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.0575171017515884E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.698236341081924E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3209,7 +3652,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EE9F-4D14-BB48-AB17F2A2858E}"/>
+              <c16:uniqueId val="{00000000-31E7-4C62-A342-719695DFF846}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3221,20 +3664,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3242,18 +3691,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$X$7:$X$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
+              <c:f>Summary!$F$2:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.4645084017331878E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6281926722371171E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.7864442032916658E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.8666059247949992E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.1155725326463128E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.0493906350223548E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3261,7 +3719,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EE9F-4D14-BB48-AB17F2A2858E}"/>
+              <c16:uniqueId val="{00000001-31E7-4C62-A342-719695DFF846}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3273,20 +3731,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3294,18 +3758,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$V$7:$V$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>1.913265306122014E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.3435905612244881</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-6.73916135204081</c:v>
+              <c:f>Summary!$H$2:$H$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.4892733172351099E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.9277214317949312E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5851718120959848E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.4650179315492281E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.7787808978270542E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.8747592328950538E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3313,7 +3786,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-EE9F-4D14-BB48-AB17F2A2858E}"/>
+              <c16:uniqueId val="{00000002-31E7-4C62-A342-719695DFF846}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3325,20 +3798,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3346,18 +3825,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$N$7:$N$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>4.9372608418367392</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.5815529336734708</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16.02264987244898</c:v>
+              <c:f>Summary!$J$2:$J$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.3533630678889111E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.81340808661066E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1838779541614279E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.029341985197206E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.4394631876350249E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.6568265682656682E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3365,7 +3853,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-EE9F-4D14-BB48-AB17F2A2858E}"/>
+              <c16:uniqueId val="{00000003-31E7-4C62-A342-719695DFF846}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3377,20 +3865,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3398,18 +3892,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$L$7:$L$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>0.23533163265306101</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.4821428571427049E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.54703124999999986</c:v>
+              <c:f>Summary!$L$2:$L$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>3.1755549433249469E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7685277990683941E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.004552845551419E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.2528479972148799E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.5086397219524111E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.9376325726600547E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3417,7 +3920,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-EE9F-4D14-BB48-AB17F2A2858E}"/>
+              <c16:uniqueId val="{00000004-31E7-4C62-A342-719695DFF846}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3429,20 +3932,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3450,18 +3959,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$T$7:$T$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>3.6485969387755119</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-6.523517219387756</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.164642857142869</c:v>
+              <c:f>Summary!$N$2:$N$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5.355837312695364E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7025222998373978E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.3476035005699564E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.1537600530638167E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.5888174423564807E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.5973075679170582E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3469,7 +3987,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-EE9F-4D14-BB48-AB17F2A2858E}"/>
+              <c16:uniqueId val="{00000005-31E7-4C62-A342-719695DFF846}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3481,20 +3999,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3502,18 +4026,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$P$7:$P$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>2.606823979590445E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.0487882653071669E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.1058673469422047E-2</c:v>
+              <c:f>Summary!$P$2:$P$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>4.562965260545949E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.551660627414955E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.211002700795591E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.260529821684623E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.6065614721678251E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.6347107438017361E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3521,7 +4054,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-EE9F-4D14-BB48-AB17F2A2858E}"/>
+              <c16:uniqueId val="{00000006-31E7-4C62-A342-719695DFF846}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3533,20 +4066,26 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>Summary!$B$7:$B$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
+              <c:f>Summary!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3554,18 +4093,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Summary!$R$7:$R$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
+              <c:f>Summary!$R$2:$R$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.7232381439227642E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7323679591510899E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.4278635052061629E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.0864533696393372E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.0504521656354171E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.9648075552387566E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3573,7 +4121,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-EE9F-4D14-BB48-AB17F2A2858E}"/>
+              <c16:uniqueId val="{00000007-31E7-4C62-A342-719695DFF846}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3640,7 +4188,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Delta MiB</a:t>
+                  <a:t>Total Cores</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -3712,15 +4260,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>609599</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>523874</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3748,16 +4296,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3782,83 +4330,6 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
@@ -3874,10 +4345,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3889,7 +4360,79 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4185,10 +4728,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4267,629 +4810,1229 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>2.4645084017331878E-4</v>
+      </c>
+      <c r="F2">
+        <v>2.4645084017331878E-4</v>
+      </c>
+      <c r="G2">
+        <v>2.4892733172351099E-4</v>
+      </c>
+      <c r="H2">
+        <v>2.4892733172351099E-4</v>
+      </c>
+      <c r="I2">
+        <v>2.3533630678889111E-4</v>
+      </c>
+      <c r="J2">
+        <v>2.3533630678889111E-4</v>
+      </c>
+      <c r="K2">
+        <v>3.1755549433249469E-3</v>
+      </c>
+      <c r="L2">
+        <v>3.1755549433249469E-3</v>
+      </c>
+      <c r="M2">
+        <v>5.355837312695364E-3</v>
+      </c>
+      <c r="N2">
+        <v>5.355837312695364E-3</v>
+      </c>
+      <c r="O2">
+        <v>4.562965260545949E-3</v>
+      </c>
+      <c r="P2">
+        <v>4.562965260545949E-3</v>
+      </c>
+      <c r="Q2">
+        <v>2.7232381439227642E-4</v>
+      </c>
+      <c r="R2">
+        <v>2.7232381439227642E-4</v>
+      </c>
+      <c r="S2">
+        <v>5.28125</v>
+      </c>
+      <c r="T2">
+        <v>5.28125</v>
+      </c>
+      <c r="U2">
+        <v>27.06640625</v>
+      </c>
+      <c r="V2">
+        <v>27.06640625</v>
+      </c>
+      <c r="W2">
+        <v>25.72265625</v>
+      </c>
+      <c r="X2">
+        <v>25.72265625</v>
+      </c>
+      <c r="Y2">
+        <v>27.45703125</v>
+      </c>
+      <c r="Z2">
+        <v>27.45703125</v>
+      </c>
+      <c r="AA2">
+        <v>25.5390625</v>
+      </c>
+      <c r="AB2">
+        <v>25.5390625</v>
+      </c>
+      <c r="AC2">
+        <v>109.58203125</v>
+      </c>
+      <c r="AD2">
+        <v>109.58203125</v>
+      </c>
+      <c r="AE2">
+        <v>456.3359375</v>
+      </c>
+      <c r="AF2">
+        <v>456.3359375</v>
+      </c>
+      <c r="AG2">
+        <v>30.9140625</v>
+      </c>
+      <c r="AH2">
+        <v>30.9140625</v>
+      </c>
+    </row>
+    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>25.881696428571431</v>
-      </c>
-      <c r="D2">
-        <v>26.027503188775508</v>
-      </c>
-      <c r="E2">
-        <v>435.4891581632653</v>
-      </c>
-      <c r="F2">
-        <v>27.51171875</v>
-      </c>
-      <c r="G2">
-        <v>91.722815688775512</v>
-      </c>
-      <c r="H2">
-        <v>50.75</v>
-      </c>
-      <c r="I2">
-        <v>285.7734375</v>
-      </c>
-      <c r="J2">
-        <v>5.4788743622448983</v>
+      <c r="C3">
+        <v>2.5576446240656781E-6</v>
+      </c>
+      <c r="D3">
+        <v>2.5576446240656781E-6</v>
+      </c>
+      <c r="E3">
+        <v>2.6281926722371171E-4</v>
+      </c>
+      <c r="F3">
+        <v>2.6281926722371171E-4</v>
+      </c>
+      <c r="G3">
+        <v>2.9277214317949312E-4</v>
+      </c>
+      <c r="H3">
+        <v>2.9277214317949312E-4</v>
+      </c>
+      <c r="I3">
+        <v>1.7819026182058889E-4</v>
+      </c>
+      <c r="J3">
+        <v>1.81340808661066E-4</v>
+      </c>
+      <c r="K3">
+        <v>2.4688752071162961E-3</v>
+      </c>
+      <c r="L3">
+        <v>2.7685277990683941E-3</v>
+      </c>
+      <c r="M3">
+        <v>5.6791239340531936E-3</v>
+      </c>
+      <c r="N3">
+        <v>5.7025222998373978E-3</v>
+      </c>
+      <c r="O3">
+        <v>4.551660627414955E-3</v>
+      </c>
+      <c r="P3">
+        <v>4.551660627414955E-3</v>
+      </c>
+      <c r="Q3">
+        <v>2.7323679591510899E-4</v>
+      </c>
+      <c r="R3">
+        <v>2.7323679591510899E-4</v>
+      </c>
+      <c r="S3">
+        <v>5.28125</v>
+      </c>
+      <c r="T3">
+        <v>5.28125</v>
+      </c>
+      <c r="U3">
+        <v>27.06640625</v>
+      </c>
+      <c r="V3">
+        <v>27.06640625</v>
+      </c>
+      <c r="W3">
+        <v>25.72265625</v>
+      </c>
+      <c r="X3">
+        <v>25.72265625</v>
+      </c>
+      <c r="Y3">
+        <v>27.45703125</v>
+      </c>
+      <c r="Z3">
+        <v>27.45703125</v>
+      </c>
+      <c r="AA3">
+        <v>25.5390625</v>
+      </c>
+      <c r="AB3">
+        <v>25.5390625</v>
+      </c>
+      <c r="AC3">
+        <v>109.2044270833333</v>
+      </c>
+      <c r="AD3">
+        <v>109.2421875</v>
+      </c>
+      <c r="AE3">
+        <v>456.359375</v>
+      </c>
+      <c r="AF3">
+        <v>456.359375</v>
+      </c>
+      <c r="AG3">
+        <v>30.9140625</v>
+      </c>
+      <c r="AH3">
+        <v>30.9140625</v>
+      </c>
+      <c r="AI3">
+        <v>2.5576446240656781E-6</v>
+      </c>
+      <c r="AJ3">
+        <v>2.5576446240656781E-6</v>
+      </c>
+      <c r="AK3">
+        <v>1.6368427050392881E-5</v>
+      </c>
+      <c r="AL3">
+        <v>1.6368427050392881E-5</v>
+      </c>
+      <c r="AM3">
+        <v>4.3844811455982021E-5</v>
+      </c>
+      <c r="AN3">
+        <v>4.3844811455982021E-5</v>
+      </c>
+      <c r="AO3">
+        <v>-5.7146044968302219E-5</v>
+      </c>
+      <c r="AP3">
+        <v>-5.3995498127825081E-5</v>
+      </c>
+      <c r="AQ3">
+        <v>-7.0667973620865175E-4</v>
+      </c>
+      <c r="AR3">
+        <v>-4.0702714425655371E-4</v>
+      </c>
+      <c r="AS3">
+        <v>3.2328662135783053E-4</v>
+      </c>
+      <c r="AT3">
+        <v>3.4668498714203379E-4</v>
+      </c>
+      <c r="AU3">
+        <v>-1.130463313099399E-5</v>
+      </c>
+      <c r="AV3">
+        <v>-1.130463313099399E-5</v>
+      </c>
+      <c r="AW3">
+        <v>9.1298152283262246E-7</v>
+      </c>
+      <c r="AX3">
+        <v>9.1298152283262246E-7</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>-0.3776041666666714</v>
+      </c>
+      <c r="BJ3">
+        <v>-0.33984375</v>
+      </c>
+      <c r="BK3">
+        <v>2.34375E-2</v>
+      </c>
+      <c r="BL3">
+        <v>2.34375E-2</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>26.72688137755102</v>
-      </c>
-      <c r="D3">
-        <v>34.113759566326529</v>
-      </c>
-      <c r="E3">
-        <v>436.16171077806121</v>
-      </c>
-      <c r="F3">
-        <v>27.51171875</v>
-      </c>
-      <c r="G3">
-        <v>93.846061862244895</v>
-      </c>
-      <c r="H3">
-        <v>50.75</v>
-      </c>
-      <c r="I3">
-        <v>285.79639668367349</v>
-      </c>
-      <c r="J3">
-        <v>6.0718670280612246</v>
-      </c>
-      <c r="K3">
-        <v>0.84518494897959329</v>
-      </c>
-      <c r="L3">
-        <v>0.84518494897959329</v>
-      </c>
-      <c r="M3">
-        <v>8.0862563775510168</v>
-      </c>
-      <c r="N3">
-        <v>8.0862563775510168</v>
-      </c>
-      <c r="O3">
-        <v>0.67255261479590445</v>
-      </c>
-      <c r="P3">
-        <v>0.67255261479590445</v>
-      </c>
-      <c r="Q3">
+      <c r="C4">
+        <v>1.8883805832244099E-4</v>
+      </c>
+      <c r="D4">
+        <v>3.5879231081263792E-4</v>
+      </c>
+      <c r="E4">
+        <v>2.7864442032916658E-4</v>
+      </c>
+      <c r="F4">
+        <v>2.7864442032916658E-4</v>
+      </c>
+      <c r="G4">
+        <v>2.5539690124571322E-4</v>
+      </c>
+      <c r="H4">
+        <v>2.5851718120959848E-4</v>
+      </c>
+      <c r="I4">
+        <v>2.1838779541614279E-4</v>
+      </c>
+      <c r="J4">
+        <v>2.1838779541614279E-4</v>
+      </c>
+      <c r="K4">
+        <v>9.2481117442260868E-3</v>
+      </c>
+      <c r="L4">
+        <v>1.004552845551419E-2</v>
+      </c>
+      <c r="M4">
+        <v>5.3476035005699564E-3</v>
+      </c>
+      <c r="N4">
+        <v>5.3476035005699564E-3</v>
+      </c>
+      <c r="O4">
+        <v>3.211002700795591E-3</v>
+      </c>
+      <c r="P4">
+        <v>3.211002700795591E-3</v>
+      </c>
+      <c r="Q4">
+        <v>2.4278635052061629E-4</v>
+      </c>
+      <c r="R4">
+        <v>2.4278635052061629E-4</v>
+      </c>
+      <c r="S4">
+        <v>7.033203125</v>
+      </c>
+      <c r="T4">
+        <v>8.6099609375000004</v>
+      </c>
+      <c r="U4">
+        <v>27.06640625</v>
+      </c>
+      <c r="V4">
+        <v>27.06640625</v>
+      </c>
+      <c r="W4">
+        <v>25.72265625</v>
+      </c>
+      <c r="X4">
+        <v>25.72265625</v>
+      </c>
+      <c r="Y4">
+        <v>27.45703125</v>
+      </c>
+      <c r="Z4">
+        <v>27.45703125</v>
+      </c>
+      <c r="AA4">
+        <v>30.9140625</v>
+      </c>
+      <c r="AB4">
+        <v>30.9140625</v>
+      </c>
+      <c r="AC4">
+        <v>109.28515625</v>
+      </c>
+      <c r="AD4">
+        <v>109.28515625</v>
+      </c>
+      <c r="AE4">
+        <v>456.38671875</v>
+      </c>
+      <c r="AF4">
+        <v>456.38671875</v>
+      </c>
+      <c r="AG4">
+        <v>30.9140625</v>
+      </c>
+      <c r="AH4">
+        <v>30.9140625</v>
+      </c>
+      <c r="AI4">
+        <v>1.8628041369837529E-4</v>
+      </c>
+      <c r="AJ4">
+        <v>3.5623466618857222E-4</v>
+      </c>
+      <c r="AK4">
+        <v>1.582515310545487E-5</v>
+      </c>
+      <c r="AL4">
+        <v>1.582515310545487E-5</v>
+      </c>
+      <c r="AM4">
+        <v>-3.7375241933779841E-5</v>
+      </c>
+      <c r="AN4">
+        <v>-3.4254961969894578E-5</v>
+      </c>
+      <c r="AO4">
+        <v>4.0197533595553927E-5</v>
+      </c>
+      <c r="AP4">
+        <v>3.7046986755076788E-5</v>
+      </c>
+      <c r="AQ4">
+        <v>6.7792365371097917E-3</v>
+      </c>
+      <c r="AR4">
+        <v>7.2770006564457966E-3</v>
+      </c>
+      <c r="AS4">
+        <v>-3.3152043348323902E-4</v>
+      </c>
+      <c r="AT4">
+        <v>-3.5491879926744218E-4</v>
+      </c>
+      <c r="AU4">
+        <v>-1.340657926619364E-3</v>
+      </c>
+      <c r="AV4">
+        <v>-1.340657926619364E-3</v>
+      </c>
+      <c r="AW4">
+        <v>-3.0450445394492641E-5</v>
+      </c>
+      <c r="AX4">
+        <v>-3.0450445394492641E-5</v>
+      </c>
+      <c r="AY4">
+        <v>1.751953125</v>
+      </c>
+      <c r="AZ4">
+        <v>3.3287109374999999</v>
+      </c>
+      <c r="BA4">
         <v>0</v>
       </c>
-      <c r="R3">
+      <c r="BB4">
         <v>0</v>
       </c>
-      <c r="S3">
-        <v>2.1232461734693828</v>
-      </c>
-      <c r="T3">
-        <v>2.1232461734693828</v>
-      </c>
-      <c r="U3">
+      <c r="BC4">
         <v>0</v>
       </c>
-      <c r="V3">
+      <c r="BD4">
         <v>0</v>
       </c>
-      <c r="W3">
-        <v>2.2959183673492589E-2</v>
-      </c>
-      <c r="X3">
-        <v>2.2959183673492589E-2</v>
-      </c>
-      <c r="Y3">
-        <v>0.59299266581632626</v>
-      </c>
-      <c r="Z3">
-        <v>0.59299266581632626</v>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>5.375</v>
+      </c>
+      <c r="BH4">
+        <v>5.375</v>
+      </c>
+      <c r="BI4">
+        <v>8.0729166666671404E-2</v>
+      </c>
+      <c r="BJ4">
+        <v>4.296875E-2</v>
+      </c>
+      <c r="BK4">
+        <v>2.734375E-2</v>
+      </c>
+      <c r="BL4">
+        <v>2.734375E-2</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>26.781489158163261</v>
-      </c>
-      <c r="D4">
-        <v>39.208625637755112</v>
-      </c>
-      <c r="E4">
-        <v>436.4153380102041</v>
-      </c>
-      <c r="F4">
-        <v>27.51171875</v>
-      </c>
-      <c r="G4">
-        <v>94.969308035714292</v>
-      </c>
-      <c r="H4">
-        <v>50.75</v>
-      </c>
-      <c r="I4">
-        <v>285.8250956632653</v>
-      </c>
-      <c r="J4">
-        <v>6.1774553571428568</v>
-      </c>
-      <c r="K4">
-        <v>5.4607780612244028E-2</v>
-      </c>
-      <c r="L4">
-        <v>5.4607780612244028E-2</v>
-      </c>
-      <c r="M4">
-        <v>5.0948660714285774</v>
-      </c>
-      <c r="N4">
-        <v>5.0948660714285774</v>
-      </c>
-      <c r="O4">
-        <v>0.25362723214288962</v>
-      </c>
-      <c r="P4">
-        <v>0.25362723214288962</v>
-      </c>
-      <c r="Q4">
+      <c r="C5">
+        <v>5.6957569457569428E-4</v>
+      </c>
+      <c r="D5">
+        <v>5.6957569457569428E-4</v>
+      </c>
+      <c r="E5">
+        <v>2.8666059247949992E-4</v>
+      </c>
+      <c r="F5">
+        <v>2.8666059247949992E-4</v>
+      </c>
+      <c r="G5">
+        <v>2.4650179315492281E-4</v>
+      </c>
+      <c r="H5">
+        <v>2.4650179315492281E-4</v>
+      </c>
+      <c r="I5">
+        <v>1.029341985197206E-3</v>
+      </c>
+      <c r="J5">
+        <v>1.029341985197206E-3</v>
+      </c>
+      <c r="K5">
+        <v>7.2528479972148799E-3</v>
+      </c>
+      <c r="L5">
+        <v>7.2528479972148799E-3</v>
+      </c>
+      <c r="M5">
+        <v>6.1537600530638167E-3</v>
+      </c>
+      <c r="N5">
+        <v>6.1537600530638167E-3</v>
+      </c>
+      <c r="O5">
+        <v>3.260529821684623E-3</v>
+      </c>
+      <c r="P5">
+        <v>3.260529821684623E-3</v>
+      </c>
+      <c r="Q5">
+        <v>3.0864533696393372E-4</v>
+      </c>
+      <c r="R5">
+        <v>3.0864533696393372E-4</v>
+      </c>
+      <c r="S5">
+        <v>8.91015625</v>
+      </c>
+      <c r="T5">
+        <v>8.91015625</v>
+      </c>
+      <c r="U5">
+        <v>27.06640625</v>
+      </c>
+      <c r="V5">
+        <v>27.06640625</v>
+      </c>
+      <c r="W5">
+        <v>25.72265625</v>
+      </c>
+      <c r="X5">
+        <v>25.72265625</v>
+      </c>
+      <c r="Y5">
+        <v>29.33203125</v>
+      </c>
+      <c r="Z5">
+        <v>29.33203125</v>
+      </c>
+      <c r="AA5">
+        <v>30.78125</v>
+      </c>
+      <c r="AB5">
+        <v>30.78125</v>
+      </c>
+      <c r="AC5">
+        <v>109.31640625</v>
+      </c>
+      <c r="AD5">
+        <v>109.31640625</v>
+      </c>
+      <c r="AE5">
+        <v>456.40234375</v>
+      </c>
+      <c r="AF5">
+        <v>456.40234375</v>
+      </c>
+      <c r="AG5">
+        <v>30.921875</v>
+      </c>
+      <c r="AH5">
+        <v>30.921875</v>
+      </c>
+      <c r="AI5">
+        <v>3.8073763625325318E-4</v>
+      </c>
+      <c r="AJ5">
+        <v>2.1078338376305641E-4</v>
+      </c>
+      <c r="AK5">
+        <v>8.016172150333335E-6</v>
+      </c>
+      <c r="AL5">
+        <v>8.016172150333335E-6</v>
+      </c>
+      <c r="AM5">
+        <v>-8.8951080907904707E-6</v>
+      </c>
+      <c r="AN5">
+        <v>-1.201538805467573E-5</v>
+      </c>
+      <c r="AO5">
+        <v>8.1095418978106295E-4</v>
+      </c>
+      <c r="AP5">
+        <v>8.1095418978106295E-4</v>
+      </c>
+      <c r="AQ5">
+        <v>-1.995263747011207E-3</v>
+      </c>
+      <c r="AR5">
+        <v>-2.79268045829931E-3</v>
+      </c>
+      <c r="AS5">
+        <v>8.0615655249386114E-4</v>
+      </c>
+      <c r="AT5">
+        <v>8.0615655249386114E-4</v>
+      </c>
+      <c r="AU5">
+        <v>4.9527120889032022E-5</v>
+      </c>
+      <c r="AV5">
+        <v>4.9527120889032022E-5</v>
+      </c>
+      <c r="AW5">
+        <v>6.5858986443317321E-5</v>
+      </c>
+      <c r="AX5">
+        <v>6.5858986443317321E-5</v>
+      </c>
+      <c r="AY5">
+        <v>1.876953125</v>
+      </c>
+      <c r="AZ5">
+        <v>0.30019531249999959</v>
+      </c>
+      <c r="BA5">
         <v>0</v>
       </c>
-      <c r="R4">
+      <c r="BB5">
         <v>0</v>
       </c>
-      <c r="S4">
-        <v>1.123246173469397</v>
-      </c>
-      <c r="T4">
-        <v>1.123246173469397</v>
-      </c>
-      <c r="U4">
+      <c r="BC5">
         <v>0</v>
       </c>
-      <c r="V4">
+      <c r="BD5">
         <v>0</v>
       </c>
-      <c r="W4">
-        <v>2.869897959180889E-2</v>
-      </c>
-      <c r="X4">
-        <v>2.869897959180889E-2</v>
-      </c>
-      <c r="Y4">
-        <v>0.1055883290816322</v>
-      </c>
-      <c r="Z4">
-        <v>0.1055883290816322</v>
+      <c r="BE5">
+        <v>1.875</v>
+      </c>
+      <c r="BF5">
+        <v>1.875</v>
+      </c>
+      <c r="BG5">
+        <v>-0.1328125</v>
+      </c>
+      <c r="BH5">
+        <v>-0.1328125</v>
+      </c>
+      <c r="BI5">
+        <v>3.125E-2</v>
+      </c>
+      <c r="BJ5">
+        <v>3.125E-2</v>
+      </c>
+      <c r="BK5">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="BL5">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="BM5">
+        <v>7.8125E-3</v>
+      </c>
+      <c r="BN5">
+        <v>7.8125E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6">
         <v>4</v>
       </c>
-      <c r="C5">
-        <v>27.28308354591837</v>
-      </c>
-      <c r="D5">
-        <v>46.451849489795919</v>
-      </c>
-      <c r="E5">
-        <v>436.43829719387747</v>
-      </c>
-      <c r="F5">
-        <v>27.51171875</v>
-      </c>
-      <c r="G5">
-        <v>96.023278061224488</v>
-      </c>
-      <c r="H5">
-        <v>50.75</v>
-      </c>
-      <c r="I5">
-        <v>285.83227040816331</v>
-      </c>
-      <c r="J5">
-        <v>6.3431122448979593</v>
-      </c>
-      <c r="K5">
-        <v>0.50159438775510168</v>
-      </c>
-      <c r="L5">
-        <v>0.50159438775510168</v>
-      </c>
-      <c r="M5">
-        <v>7.2432238520408134</v>
-      </c>
-      <c r="N5">
-        <v>7.2432238520408134</v>
-      </c>
-      <c r="O5">
-        <v>2.2959183673435749E-2</v>
-      </c>
-      <c r="P5">
-        <v>2.2959183673435749E-2</v>
-      </c>
-      <c r="Q5">
+      <c r="C6">
+        <v>5.0575171017515884E-4</v>
+      </c>
+      <c r="D6">
+        <v>5.0575171017515884E-4</v>
+      </c>
+      <c r="E6">
+        <v>3.1155725326463128E-4</v>
+      </c>
+      <c r="F6">
+        <v>3.1155725326463128E-4</v>
+      </c>
+      <c r="G6">
+        <v>2.7787808978270542E-4</v>
+      </c>
+      <c r="H6">
+        <v>2.7787808978270542E-4</v>
+      </c>
+      <c r="I6">
+        <v>2.4394631876350249E-3</v>
+      </c>
+      <c r="J6">
+        <v>2.4394631876350249E-3</v>
+      </c>
+      <c r="K6">
+        <v>3.5086397219524111E-3</v>
+      </c>
+      <c r="L6">
+        <v>3.5086397219524111E-3</v>
+      </c>
+      <c r="M6">
+        <v>7.5888174423564807E-3</v>
+      </c>
+      <c r="N6">
+        <v>7.5888174423564807E-3</v>
+      </c>
+      <c r="O6">
+        <v>3.6065614721678251E-3</v>
+      </c>
+      <c r="P6">
+        <v>3.6065614721678251E-3</v>
+      </c>
+      <c r="Q6">
+        <v>4.0504521656354171E-4</v>
+      </c>
+      <c r="R6">
+        <v>4.0504521656354171E-4</v>
+      </c>
+      <c r="S6">
+        <v>9.21484375</v>
+      </c>
+      <c r="T6">
+        <v>9.21484375</v>
+      </c>
+      <c r="U6">
+        <v>27.06640625</v>
+      </c>
+      <c r="V6">
+        <v>27.06640625</v>
+      </c>
+      <c r="W6">
+        <v>25.72265625</v>
+      </c>
+      <c r="X6">
+        <v>25.72265625</v>
+      </c>
+      <c r="Y6">
+        <v>29.51953125</v>
+      </c>
+      <c r="Z6">
+        <v>29.51953125</v>
+      </c>
+      <c r="AA6">
+        <v>30.3671875</v>
+      </c>
+      <c r="AB6">
+        <v>30.3671875</v>
+      </c>
+      <c r="AC6">
+        <v>109.48046875</v>
+      </c>
+      <c r="AD6">
+        <v>109.48046875</v>
+      </c>
+      <c r="AE6">
+        <v>456.44140625</v>
+      </c>
+      <c r="AF6">
+        <v>456.44140625</v>
+      </c>
+      <c r="AG6">
+        <v>30.92578125</v>
+      </c>
+      <c r="AH6">
+        <v>30.92578125</v>
+      </c>
+      <c r="AI6">
+        <v>-6.382398440053544E-5</v>
+      </c>
+      <c r="AJ6">
+        <v>-6.382398440053544E-5</v>
+      </c>
+      <c r="AK6">
+        <v>2.4896660785131419E-5</v>
+      </c>
+      <c r="AL6">
+        <v>2.4896660785131419E-5</v>
+      </c>
+      <c r="AM6">
+        <v>3.1376296627782672E-5</v>
+      </c>
+      <c r="AN6">
+        <v>3.1376296627782672E-5</v>
+      </c>
+      <c r="AO6">
+        <v>1.4101212024378201E-3</v>
+      </c>
+      <c r="AP6">
+        <v>1.4101212024378201E-3</v>
+      </c>
+      <c r="AQ6">
+        <v>-3.7442082752624688E-3</v>
+      </c>
+      <c r="AR6">
+        <v>-3.7442082752624688E-3</v>
+      </c>
+      <c r="AS6">
+        <v>1.4350573892926641E-3</v>
+      </c>
+      <c r="AT6">
+        <v>1.4350573892926641E-3</v>
+      </c>
+      <c r="AU6">
+        <v>3.4603165048320209E-4</v>
+      </c>
+      <c r="AV6">
+        <v>3.4603165048320209E-4</v>
+      </c>
+      <c r="AW6">
+        <v>9.639987959960799E-5</v>
+      </c>
+      <c r="AX6">
+        <v>9.639987959960799E-5</v>
+      </c>
+      <c r="AY6">
+        <v>0.3046875</v>
+      </c>
+      <c r="AZ6">
+        <v>0.3046875</v>
+      </c>
+      <c r="BA6">
         <v>0</v>
       </c>
-      <c r="R5">
+      <c r="BB6">
         <v>0</v>
       </c>
-      <c r="S5">
-        <v>1.053970025510196</v>
-      </c>
-      <c r="T5">
-        <v>1.053970025510196</v>
-      </c>
-      <c r="U5">
+      <c r="BC6">
         <v>0</v>
       </c>
-      <c r="V5">
+      <c r="BD6">
         <v>0</v>
       </c>
-      <c r="W5">
-        <v>7.1747448979522233E-3</v>
-      </c>
-      <c r="X5">
-        <v>7.1747448979522233E-3</v>
-      </c>
-      <c r="Y5">
-        <v>0.16565688775510259</v>
-      </c>
-      <c r="Z5">
-        <v>0.16565688775510259</v>
+      <c r="BE6">
+        <v>0.1875</v>
+      </c>
+      <c r="BF6">
+        <v>0.1875</v>
+      </c>
+      <c r="BG6">
+        <v>-0.4140625</v>
+      </c>
+      <c r="BH6">
+        <v>-0.4140625</v>
+      </c>
+      <c r="BI6">
+        <v>0.1640625</v>
+      </c>
+      <c r="BJ6">
+        <v>0.1640625</v>
+      </c>
+      <c r="BK6">
+        <v>3.90625E-2</v>
+      </c>
+      <c r="BL6">
+        <v>3.90625E-2</v>
+      </c>
+      <c r="BM6">
+        <v>3.90625E-3</v>
+      </c>
+      <c r="BN6">
+        <v>3.90625E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7">
         <v>5</v>
       </c>
-      <c r="C6">
-        <v>27.393255739795919</v>
-      </c>
-      <c r="D6">
-        <v>48.628587372448983</v>
-      </c>
-      <c r="E6">
-        <v>436.4583067602041</v>
-      </c>
-      <c r="F6">
-        <v>27.51171875</v>
-      </c>
-      <c r="G6">
-        <v>95.146125637755105</v>
-      </c>
-      <c r="H6">
-        <v>50.75</v>
-      </c>
-      <c r="I6">
-        <v>285.83801020408163</v>
-      </c>
-      <c r="J6">
-        <v>6.3773118622448983</v>
-      </c>
-      <c r="K6">
-        <v>0.1101721938775526</v>
-      </c>
-      <c r="L6">
-        <v>0.1101721938775526</v>
-      </c>
-      <c r="M6">
-        <v>2.176737882653057</v>
-      </c>
-      <c r="N6">
-        <v>2.176737882653057</v>
-      </c>
-      <c r="O6">
-        <v>2.0009566326564251E-2</v>
-      </c>
-      <c r="P6">
-        <v>2.0009566326564251E-2</v>
-      </c>
-      <c r="Q6">
+      <c r="C7">
+        <v>4.698236341081924E-4</v>
+      </c>
+      <c r="D7">
+        <v>4.698236341081924E-4</v>
+      </c>
+      <c r="E7">
+        <v>3.0493906350223548E-4</v>
+      </c>
+      <c r="F7">
+        <v>3.0493906350223548E-4</v>
+      </c>
+      <c r="G7">
+        <v>2.8747592328950538E-4</v>
+      </c>
+      <c r="H7">
+        <v>2.8747592328950538E-4</v>
+      </c>
+      <c r="I7">
+        <v>4.6568265682656682E-3</v>
+      </c>
+      <c r="J7">
+        <v>4.6568265682656682E-3</v>
+      </c>
+      <c r="K7">
+        <v>3.9376325726600547E-3</v>
+      </c>
+      <c r="L7">
+        <v>3.9376325726600547E-3</v>
+      </c>
+      <c r="M7">
+        <v>9.5973075679170582E-3</v>
+      </c>
+      <c r="N7">
+        <v>9.5973075679170582E-3</v>
+      </c>
+      <c r="O7">
+        <v>3.6347107438017361E-3</v>
+      </c>
+      <c r="P7">
+        <v>3.6347107438017361E-3</v>
+      </c>
+      <c r="Q7">
+        <v>4.9648075552387566E-4</v>
+      </c>
+      <c r="R7">
+        <v>4.9648075552387566E-4</v>
+      </c>
+      <c r="S7">
+        <v>9.29296875</v>
+      </c>
+      <c r="T7">
+        <v>9.29296875</v>
+      </c>
+      <c r="U7">
+        <v>27.06640625</v>
+      </c>
+      <c r="V7">
+        <v>27.06640625</v>
+      </c>
+      <c r="W7">
+        <v>25.72265625</v>
+      </c>
+      <c r="X7">
+        <v>25.72265625</v>
+      </c>
+      <c r="Y7">
+        <v>29.703125</v>
+      </c>
+      <c r="Z7">
+        <v>29.703125</v>
+      </c>
+      <c r="AA7">
+        <v>31.09375</v>
+      </c>
+      <c r="AB7">
+        <v>31.09375</v>
+      </c>
+      <c r="AC7">
+        <v>109.390625</v>
+      </c>
+      <c r="AD7">
+        <v>109.390625</v>
+      </c>
+      <c r="AE7">
+        <v>456.45703125</v>
+      </c>
+      <c r="AF7">
+        <v>456.45703125</v>
+      </c>
+      <c r="AG7">
+        <v>30.9296875</v>
+      </c>
+      <c r="AH7">
+        <v>30.9296875</v>
+      </c>
+      <c r="AI7">
+        <v>-3.5928076066966432E-5</v>
+      </c>
+      <c r="AJ7">
+        <v>-3.5928076066966432E-5</v>
+      </c>
+      <c r="AK7">
+        <v>-6.618189762395857E-6</v>
+      </c>
+      <c r="AL7">
+        <v>-6.618189762395857E-6</v>
+      </c>
+      <c r="AM7">
+        <v>9.5978335067999532E-6</v>
+      </c>
+      <c r="AN7">
+        <v>9.5978335067999532E-6</v>
+      </c>
+      <c r="AO7">
+        <v>2.2173633806306429E-3</v>
+      </c>
+      <c r="AP7">
+        <v>2.2173633806306429E-3</v>
+      </c>
+      <c r="AQ7">
+        <v>4.2899285070764409E-4</v>
+      </c>
+      <c r="AR7">
+        <v>4.2899285070764409E-4</v>
+      </c>
+      <c r="AS7">
+        <v>2.0084901255605771E-3</v>
+      </c>
+      <c r="AT7">
+        <v>2.0084901255605771E-3</v>
+      </c>
+      <c r="AU7">
+        <v>2.814927163391099E-5</v>
+      </c>
+      <c r="AV7">
+        <v>2.814927163391099E-5</v>
+      </c>
+      <c r="AW7">
+        <v>9.1435538960333998E-5</v>
+      </c>
+      <c r="AX7">
+        <v>9.1435538960333998E-5</v>
+      </c>
+      <c r="AY7">
+        <v>7.8125E-2</v>
+      </c>
+      <c r="AZ7">
+        <v>7.8125E-2</v>
+      </c>
+      <c r="BA7">
         <v>0</v>
       </c>
-      <c r="R6">
+      <c r="BB7">
         <v>0</v>
       </c>
-      <c r="S6">
-        <v>-0.87715242346938282</v>
-      </c>
-      <c r="T6">
-        <v>-0.87715242346938282</v>
-      </c>
-      <c r="U6">
+      <c r="BC7">
         <v>0</v>
       </c>
-      <c r="V6">
+      <c r="BD7">
         <v>0</v>
       </c>
-      <c r="W6">
-        <v>5.7397959183731473E-3</v>
-      </c>
-      <c r="X6">
-        <v>5.7397959183731473E-3</v>
-      </c>
-      <c r="Y6">
-        <v>3.4199617346938993E-2</v>
-      </c>
-      <c r="Z6">
-        <v>3.4199617346938993E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>27.894690688775508</v>
-      </c>
-      <c r="D7">
-        <v>54.735411352040813</v>
-      </c>
-      <c r="E7">
-        <v>436.49816645408163</v>
-      </c>
-      <c r="F7">
-        <v>27.51171875</v>
-      </c>
-      <c r="G7">
-        <v>107.1427774234694</v>
-      </c>
-      <c r="H7">
-        <v>50.761001275510203</v>
-      </c>
-      <c r="I7">
-        <v>285.84375</v>
-      </c>
-      <c r="J7">
-        <v>6.5682397959183669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>28.130022321428569</v>
-      </c>
-      <c r="D8">
-        <v>59.672672193877553</v>
-      </c>
-      <c r="E8">
-        <v>436.52423469387747</v>
-      </c>
-      <c r="F8">
-        <v>27.51171875</v>
-      </c>
-      <c r="G8">
-        <v>110.79137436224489</v>
-      </c>
-      <c r="H8">
-        <v>50.762914540816332</v>
-      </c>
-      <c r="I8">
-        <v>285.84375</v>
-      </c>
-      <c r="J8">
-        <v>6.6277104591836737</v>
-      </c>
-      <c r="K8">
-        <v>0.23533163265306101</v>
-      </c>
-      <c r="L8">
-        <v>0.23533163265306101</v>
-      </c>
-      <c r="M8">
-        <v>4.9372608418367392</v>
-      </c>
-      <c r="N8">
-        <v>4.9372608418367392</v>
-      </c>
-      <c r="O8">
-        <v>2.606823979590445E-2</v>
-      </c>
-      <c r="P8">
-        <v>2.606823979590445E-2</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>3.6485969387755119</v>
-      </c>
-      <c r="T8">
-        <v>3.6485969387755119</v>
-      </c>
-      <c r="U8">
-        <v>1.913265306122014E-3</v>
-      </c>
-      <c r="V8">
-        <v>1.913265306122014E-3</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>5.9470663265306811E-2</v>
-      </c>
-      <c r="Z8">
-        <v>5.9470663265306811E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>28.21484375</v>
-      </c>
-      <c r="D9">
-        <v>63.254225127551017</v>
-      </c>
-      <c r="E9">
-        <v>436.5447225765306</v>
-      </c>
-      <c r="F9">
-        <v>27.51171875</v>
-      </c>
-      <c r="G9">
-        <v>104.2678571428571</v>
-      </c>
-      <c r="H9">
-        <v>58.106505102040813</v>
-      </c>
-      <c r="I9">
-        <v>285.84375</v>
-      </c>
-      <c r="J9">
-        <v>6.7863520408163263</v>
-      </c>
-      <c r="K9">
-        <v>8.4821428571427049E-2</v>
-      </c>
-      <c r="L9">
-        <v>8.4821428571427049E-2</v>
-      </c>
-      <c r="M9">
-        <v>3.5815529336734708</v>
-      </c>
-      <c r="N9">
-        <v>3.5815529336734708</v>
-      </c>
-      <c r="O9">
-        <v>2.0487882653071669E-2</v>
-      </c>
-      <c r="P9">
-        <v>2.0487882653071669E-2</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>-6.523517219387756</v>
-      </c>
-      <c r="T9">
-        <v>-6.523517219387756</v>
-      </c>
-      <c r="U9">
-        <v>7.3435905612244881</v>
-      </c>
-      <c r="V9">
-        <v>7.3435905612244881</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0.15864158163265249</v>
-      </c>
-      <c r="Z9">
-        <v>0.15864158163265249</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10">
-        <v>5</v>
-      </c>
-      <c r="C10">
-        <v>28.761875</v>
-      </c>
-      <c r="D10">
-        <v>79.276875000000004</v>
-      </c>
-      <c r="E10">
-        <v>436.58578125000003</v>
-      </c>
-      <c r="F10">
-        <v>27.51171875</v>
-      </c>
-      <c r="G10">
-        <v>114.4325</v>
-      </c>
-      <c r="H10">
-        <v>51.367343750000003</v>
-      </c>
-      <c r="I10">
-        <v>285.84375</v>
-      </c>
-      <c r="J10">
-        <v>6.8672656249999999</v>
-      </c>
-      <c r="K10">
-        <v>0.54703124999999986</v>
-      </c>
-      <c r="L10">
-        <v>0.54703124999999986</v>
-      </c>
-      <c r="M10">
-        <v>16.02264987244898</v>
-      </c>
-      <c r="N10">
-        <v>16.02264987244898</v>
-      </c>
-      <c r="O10">
-        <v>4.1058673469422047E-2</v>
-      </c>
-      <c r="P10">
-        <v>4.1058673469422047E-2</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>10.164642857142869</v>
-      </c>
-      <c r="T10">
-        <v>10.164642857142869</v>
-      </c>
-      <c r="U10">
-        <v>-6.73916135204081</v>
-      </c>
-      <c r="V10">
-        <v>-6.73916135204081</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>8.091358418367367E-2</v>
-      </c>
-      <c r="Z10">
-        <v>8.091358418367367E-2</v>
+      <c r="BE7">
+        <v>0.18359375</v>
+      </c>
+      <c r="BF7">
+        <v>0.18359375</v>
+      </c>
+      <c r="BG7">
+        <v>0.7265625</v>
+      </c>
+      <c r="BH7">
+        <v>0.7265625</v>
+      </c>
+      <c r="BI7">
+        <v>-8.984375E-2</v>
+      </c>
+      <c r="BJ7">
+        <v>-8.984375E-2</v>
+      </c>
+      <c r="BK7">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="BL7">
+        <v>1.5625E-2</v>
+      </c>
+      <c r="BM7">
+        <v>3.90625E-3</v>
+      </c>
+      <c r="BN7">
+        <v>3.90625E-3</v>
       </c>
     </row>
   </sheetData>
@@ -4905,14 +6048,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>